--- a/local_data/arrivees_accueil.xlsx
+++ b/local_data/arrivees_accueil.xlsx
@@ -355,1810 +355,1465 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>PRIO</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>heure_arrivee</t>
+          <t>prio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>date_arrivee</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>minutes_depuis_8h</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>heure_arrivee_str</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C2" s="2">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
         <v>42320.34355087962</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>74.71326666673025</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2015-11-12 08:14:42</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C3" s="2">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
         <v>42320.3453441551</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>77.29558333158494</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2015-11-12 08:17:17</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C4" s="2">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
         <v>42320.35238643519</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>87.43646666606267</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2015-11-12 08:27:26</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C5" s="2">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
         <v>42320.36081384259</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>99.57193333307902</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2015-11-12 08:39:34</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C6" s="2">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
         <v>42320.36267498843</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>102.251983332634</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2015-11-12 08:42:15</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>42320.36401783564</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>104.1856833338738</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2015-11-12 08:44:11</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C8" s="2">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
         <v>42320.3794509375</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>126.409350001812</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:06:24</t>
-        </is>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C9" s="2">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
         <v>42320.38918754629</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>140.4300666650136</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:20:25</t>
-        </is>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C10" s="2">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
         <v>42320.39185063657</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>144.2649166663488</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:24:15</t>
-        </is>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
         <v>42320.39753402778</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>152.4490000009537</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:32:26</t>
-        </is>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C12" s="2">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
         <v>42320.40289678241</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>160.1713666677475</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:40:10</t>
-        </is>
-      </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
         <v>42320.40639071759</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>165.2026333332062</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:45:12</t>
-        </is>
-      </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C14" s="2">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
         <v>42320.40773929398</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>167.1445833325386</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2015-11-12 09:47:08</t>
-        </is>
-      </c>
-      <c r="F14">
-        <v>13</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C15" s="2">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
         <v>42320.41783260417</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>181.6789499998093</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:01:40</t>
-        </is>
-      </c>
-      <c r="F15">
-        <v>14</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C16" s="2">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
         <v>42320.42068614584</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>185.7880499998728</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:05:47</t>
-        </is>
-      </c>
-      <c r="F16">
-        <v>15</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
         <v>42320.42510060185</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>192.1448666652044</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:12:08</t>
-        </is>
-      </c>
-      <c r="F17">
-        <v>16</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C18" s="2">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D18" s="2">
         <v>42320.42736293982</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>195.4026333332062</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:15:24</t>
-        </is>
-      </c>
-      <c r="F18">
-        <v>17</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C19" s="2">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D19" s="2">
         <v>42320.43058361112</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>200.0404000004133</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:20:02</t>
-        </is>
-      </c>
-      <c r="F19">
-        <v>18</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <v>42320.43083668982</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>200.4048333326976</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:20:24</t>
-        </is>
-      </c>
-      <c r="F20">
-        <v>19</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C21" s="2">
+      <c r="D21" s="2">
         <v>42320.43828894676</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>211.1360833326976</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:31:08</t>
-        </is>
-      </c>
-      <c r="F21">
-        <v>20</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C22" s="2">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D22" s="2">
         <v>42320.44373893518</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>218.9840666651726</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:38:59</t>
-        </is>
-      </c>
-      <c r="F22">
-        <v>21</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C23" s="2">
+      <c r="D23" s="2">
         <v>42320.44883424768</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>226.3213166673978</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:46:19</t>
-        </is>
-      </c>
-      <c r="F23">
-        <v>22</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C24" s="2">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D24" s="2">
         <v>42320.45005219907</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>228.0751666665077</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:48:04</t>
-        </is>
-      </c>
-      <c r="F24">
-        <v>23</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C25" s="2">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D25" s="2">
         <v>42320.45050247685</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>228.7235666672389</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:48:43</t>
-        </is>
-      </c>
-      <c r="F25">
-        <v>24</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C26" s="2">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D26" s="2">
         <v>42320.45277435186</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>231.9950666666031</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:51:59</t>
-        </is>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C27" s="2">
+      <c r="D27" s="2">
         <v>42320.45498730324</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>235.1817166686058</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2015-11-12 10:55:10</t>
-        </is>
-      </c>
-      <c r="F27">
-        <v>26</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C28" s="2">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D28" s="2">
         <v>42320.46238083333</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>245.8283999999364</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:05:49</t>
-        </is>
-      </c>
-      <c r="F28">
-        <v>27</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C29" s="2">
+      <c r="D29" s="2">
         <v>42320.46546546296</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>250.2702666680018</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:10:16</t>
-        </is>
-      </c>
-      <c r="F29">
-        <v>28</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C30" s="2">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D30" s="2">
         <v>42320.46585837963</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>250.8360666672389</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:10:50</t>
-        </is>
-      </c>
-      <c r="F30">
-        <v>29</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C31" s="2">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D31" s="2">
         <v>42320.47567991898</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>264.979083331426</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:24:58</t>
-        </is>
-      </c>
-      <c r="F31">
-        <v>30</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C32" s="2">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D32" s="2">
         <v>42320.48366081018</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>276.4715666651726</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:36:28</t>
-        </is>
-      </c>
-      <c r="F32">
-        <v>31</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C33" s="2">
+      <c r="D33" s="2">
         <v>42320.48557564815</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>279.2289333343506</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:39:13</t>
-        </is>
-      </c>
-      <c r="F33">
-        <v>32</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D34" s="2">
         <v>42320.48966234954</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>285.1137833317121</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:45:06</t>
-        </is>
-      </c>
-      <c r="F34">
-        <v>33</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C35" s="2">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
         <v>42320.49765689815</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>296.625933333238</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2015-11-12 11:56:37</t>
-        </is>
-      </c>
-      <c r="F35">
-        <v>34</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C36" s="2">
+      <c r="D36" s="2">
         <v>42320.52372508102</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>334.1641166647275</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2015-11-12 12:34:09</t>
-        </is>
-      </c>
-      <c r="F36">
-        <v>35</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C37" s="2">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D37" s="2">
         <v>42320.52674628473</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>338.5146499991417</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2015-11-12 12:38:30</t>
-        </is>
-      </c>
-      <c r="F37">
-        <v>36</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C38" s="2">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
         <v>42320.56985648148</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>400.5933333317438</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2015-11-12 13:40:35</t>
-        </is>
-      </c>
-      <c r="F38">
-        <v>37</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C39" s="2">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D39" s="2">
         <v>42320.57597686343</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>409.4066833337148</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2015-11-12 13:49:24</t>
-        </is>
-      </c>
-      <c r="F39">
-        <v>38</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C40" s="2">
+      <c r="D40" s="2">
         <v>42320.57860665509</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>413.1935833334923</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2015-11-12 13:53:11</t>
-        </is>
-      </c>
-      <c r="F40">
-        <v>39</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C41" s="2">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
         <v>42320.58333263889</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>419.9990000009537</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2015-11-12 13:59:59</t>
-        </is>
-      </c>
-      <c r="F41">
-        <v>40</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C42" s="2">
+      <c r="D42" s="2">
         <v>42320.58667986111</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>424.8190000017484</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:04:49</t>
-        </is>
-      </c>
-      <c r="F42">
-        <v>41</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C43" s="2">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D43" s="2">
         <v>42320.5876265625</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>426.1822499990463</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:06:10</t>
-        </is>
-      </c>
-      <c r="F43">
-        <v>42</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C44" s="2">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D44" s="2">
         <v>42320.59234258102</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>432.9733166654905</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:12:58</t>
-        </is>
-      </c>
-      <c r="F44">
-        <v>43</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C45" s="2">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D45" s="2">
         <v>42320.60473890047</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>450.8240166664124</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:30:49</t>
-        </is>
-      </c>
-      <c r="F45">
-        <v>44</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C46" s="2">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D46" s="2">
         <v>42320.60767001157</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>455.0448166648547</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:35:02</t>
-        </is>
-      </c>
-      <c r="F46">
-        <v>45</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>226</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C47" s="2">
+      <c r="D47" s="2">
         <v>42320.61729995371</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>468.9119333346685</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:48:54</t>
-        </is>
-      </c>
-      <c r="F47">
-        <v>46</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C48" s="2">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D48" s="2">
         <v>42320.61741021991</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>469.0707166671753</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:49:04</t>
-        </is>
-      </c>
-      <c r="F48">
-        <v>47</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C49" s="2">
+      <c r="D49" s="2">
         <v>42320.62105298611</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>474.3162999987602</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2015-11-12 14:54:18</t>
-        </is>
-      </c>
-      <c r="F49">
-        <v>48</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C50" s="2">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D50" s="2">
         <v>42320.62810223379</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>484.4672166665395</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:04:28</t>
-        </is>
-      </c>
-      <c r="F50">
-        <v>49</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>239</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C51" s="2">
+      <c r="D51" s="2">
         <v>42320.62907663194</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>485.8703499992689</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:05:52</t>
-        </is>
-      </c>
-      <c r="F51">
-        <v>50</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C52" s="2">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D52" s="2">
         <v>42320.63070585649</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>488.2164333343506</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:08:12</t>
-        </is>
-      </c>
-      <c r="F52">
-        <v>51</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C53" s="2">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D53" s="2">
         <v>42320.64125711806</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>503.410250000159</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:23:24</t>
-        </is>
-      </c>
-      <c r="F53">
-        <v>52</v>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>255</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C54" s="2">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D54" s="2">
         <v>42320.64557057871</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>509.6216333349546</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:29:37</t>
-        </is>
-      </c>
-      <c r="F54">
-        <v>53</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>259</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C55" s="2">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D55" s="2">
         <v>42320.65291851852</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>520.2026666680972</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:40:12</t>
-        </is>
-      </c>
-      <c r="F55">
-        <v>54</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C56" s="2">
+      <c r="D56" s="2">
         <v>42320.65441134259</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>522.3523333350818</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:42:21</t>
-        </is>
-      </c>
-      <c r="F56">
-        <v>55</v>
-      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C57" s="2">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D57" s="2">
         <v>42320.65621092592</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>524.9437333345413</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:44:56</t>
-        </is>
-      </c>
-      <c r="F57">
-        <v>56</v>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>272</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C58" s="2">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D58" s="2">
         <v>42320.66294162037</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>534.6359333316485</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2015-11-12 15:54:38</t>
-        </is>
-      </c>
-      <c r="F58">
-        <v>57</v>
-      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C59" s="2">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D59" s="2">
         <v>42320.66921194445</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>543.6651999990146</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:03:39</t>
-        </is>
-      </c>
-      <c r="F59">
-        <v>58</v>
-      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C60" s="2">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D60" s="2">
         <v>42320.67239732639</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>548.2521499991417</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:08:15</t>
-        </is>
-      </c>
-      <c r="F60">
-        <v>59</v>
-      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>279</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C61" s="2">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D61" s="2">
         <v>42320.67711501157</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>555.0456166664759</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:15:02</t>
-        </is>
-      </c>
-      <c r="F61">
-        <v>60</v>
-      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C62" s="2">
+      <c r="D62" s="2">
         <v>42320.67871160879</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>557.344716668129</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:17:20</t>
-        </is>
-      </c>
-      <c r="F62">
-        <v>61</v>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>285</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C63" s="2">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D63" s="2">
         <v>42320.69086069445</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>574.8394000013669</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:34:50</t>
-        </is>
-      </c>
-      <c r="F63">
-        <v>62</v>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C64" s="2">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D64" s="2">
         <v>42320.69403168981</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>579.4056333343188</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:39:24</t>
-        </is>
-      </c>
-      <c r="F64">
-        <v>63</v>
-      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>286</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Prioritaire</t>
         </is>
       </c>
-      <c r="C65" s="2">
+      <c r="D65" s="2">
         <v>42320.69420815972</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>579.6597500006358</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2015-11-12 16:39:39</t>
-        </is>
-      </c>
-      <c r="F65">
-        <v>64</v>
-      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>293</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C66" s="2">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D66" s="2">
         <v>42320.71244462963</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>605.9202666680018</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2015-11-12 17:05:55</t>
-        </is>
-      </c>
-      <c r="F66">
-        <v>65</v>
-      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C67" s="2">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D67" s="2">
         <v>42320.72107685186</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>618.3506666660309</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2015-11-12 17:18:21</t>
-        </is>
-      </c>
-      <c r="F67">
-        <v>66</v>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>297</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C68" s="2">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D68" s="2">
         <v>42320.73307936342</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>635.63428333203</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2015-11-12 17:35:38</t>
-        </is>
-      </c>
-      <c r="F68">
-        <v>67</v>
-      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>298</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="C69" s="2">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D69" s="2">
         <v>42320.7438344213</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>651.1215666651726</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2015-11-12 17:51:07</t>
-        </is>
-      </c>
-      <c r="F69">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
